--- a/HW6/HW6_submissions/HW6_grades.xlsx
+++ b/HW6/HW6_submissions/HW6_grades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Documents/GitHub/2026_Computational-Modeling/HW6/HW6_submissions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW6/HW6_submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6EA746-A223-3D4E-AE9C-8C6F3413456A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D381E62-CCC6-6445-8A93-9A533A66E7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27060" yWindow="580" windowWidth="24140" windowHeight="25640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>No.</t>
   </si>
@@ -90,10 +90,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Score (140) </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Q5 (30 points)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -169,13 +165,888 @@
   </si>
   <si>
     <t>협동과정 인지과학전공</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (150) </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Q1
+1) individual-level raw parameter prior </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주석처리함 (-5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Q2
+Q3
+1) individual-level raw parameter prior </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주석처리함 (-5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Q4
+1) individual-level raw parameter prior </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주석처리함 (-5)
+Q5
+1) 실행 코드에서 trial loop 누락/오류 (T정의를 안함) (-4)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q1
+1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
+2a) ind posterior dist 없음 (-1)
+Q2
+1) beta prior 설정 0~5 (-1)
+Q3
+1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
+2) ind posterior dist 없음 (-1)
+Q4
+1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
+1) ind post distribution 없음 (-1)
+Q5
+1) 문제없음 
+2) 문제없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Q1
+2a) individual posterior distribution </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mean histogram </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-1)
+Q2
+1)  alpha, beta prior </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설정함 (-2.5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> scatter plot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+Q3
+2) individual posterior plot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음 (-1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Q4
+1) individual posterior plot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음 (-1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+3) individual posterior plot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">없음 (-1)
+Q5
+1) parameter range 설정이 틀림 (lambda, tau) (-1)
+2) parameter range 설정이 틀림 (lambda, tau) (-1)
+</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Q1
+2a) ind, group posterior dist </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음 (-2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Q2
+Q3
+1) ind, group posterior dis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음 (-2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Q4
+Q5
+1) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한명만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">보고 </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지각제출 
+Q1
+2a) group, ind posterior plot 보고 없음. (-2)
+Q2
+Q3
+2) group, ind posterior plot 보고 없음. (-2) 
+4) discussion 해석 반대 (-2)
+Q4
+1) group, ind posterior plot 보고 없음 (-2)
+3) group, ind posterior plot 보고 없음 (-2)
+4) 해석이 부정확함: 300 trials에서 error bar와 outlier가 줄었으므로 shrinkage가 더 커졌다고 보고함; 300trial 에서 shrinkage 는 줄었음 (-2)
+Q5
+없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Q1
+1) ind posterior dist </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-1)
+2) beta scatter plot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이 다름, seed 설정 안함 (-2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Q2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+2) scatter plot 아예 다름, seed 설정 안함 (-2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Q3
+2) ind posterior dist </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-1)
+3) scatter plot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다름, seed 설정 문제 (-2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Q4
+1) ind posterior dist </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-1)
+2) scatter plot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, seed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, simulation num_subj </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설정 문제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-4)
+3) ind posterior dist </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (-1)
+Q5
+1. lambda, tau </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>범위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반대 (-1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2. subject ID loop </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오류 (-2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+3. log-likeihood </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아닌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> likelihood </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계산 (-1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지각제출</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+Q1
+1) stan 에서 alpha_pr, beta_pr 주석 처리 (-5)
+Q2
+1) beta unifiorm prior 설정 0~5 (-1)
+Q3
+1) stan 에서 alpha_pr, beta_pr 주석 처리 (-5)
+Q4
+1) stan 에 hyperparameter(alpha_pos, alpha_neg, beta) 없음 (-2.5)
+2) 없음(-5) 
+3) group posterior dist 없음 (-2)
+4) 없음 (-10)
+Q5
+없음</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -221,6 +1092,14 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -276,7 +1155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -305,6 +1184,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,7 +1527,7 @@
         <v>15</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
@@ -654,206 +1536,324 @@
         <v>16</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="70" customHeight="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="309" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="F2" s="3">
+        <v>29</v>
+      </c>
+      <c r="G2" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="H2" s="3">
+        <v>39</v>
+      </c>
+      <c r="I2" s="3">
+        <v>28</v>
+      </c>
+      <c r="J2" s="3">
+        <v>28</v>
+      </c>
+      <c r="K2" s="3">
+        <f t="shared" ref="K2:K9" si="0">SUM(F2:J2)</f>
+        <v>141.5</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="118" customHeight="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="281" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="F3" s="3">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3">
+        <v>35</v>
+      </c>
+      <c r="I3" s="3">
+        <v>25</v>
+      </c>
+      <c r="J3" s="3">
+        <v>26</v>
+      </c>
+      <c r="K3" s="3">
+        <f t="shared" si="0"/>
+        <v>131</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="127" customHeight="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="401" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="E4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="9"/>
+        <v>26</v>
+      </c>
+      <c r="F4" s="3">
+        <v>28</v>
+      </c>
+      <c r="G4" s="3">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3">
+        <v>36</v>
+      </c>
+      <c r="I4" s="3">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="140" customHeight="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="119" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="D5" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="F5" s="3">
+        <v>30</v>
+      </c>
+      <c r="G5" s="7">
+        <v>20</v>
+      </c>
+      <c r="H5" s="7">
+        <v>40</v>
+      </c>
+      <c r="I5" s="7">
+        <v>30</v>
+      </c>
+      <c r="J5" s="7">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
       <c r="L5" s="9"/>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="48" customHeight="1">
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="359" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="E6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
         <v>27</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="6"/>
+      <c r="G6" s="3">
+        <v>18</v>
+      </c>
+      <c r="H6" s="3">
+        <v>37</v>
+      </c>
+      <c r="I6" s="3">
+        <v>24</v>
+      </c>
+      <c r="J6" s="3">
+        <v>26</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="0"/>
+        <v>132</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="44" customHeight="1">
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="244" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3">
+        <v>20</v>
+      </c>
+      <c r="H7" s="3">
         <v>38</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="I7" s="3">
+        <v>30</v>
+      </c>
+      <c r="J7" s="3">
+        <v>30</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" si="0"/>
+        <v>146</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="142" customHeight="1">
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="324" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="D8" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="F8" s="3">
+        <v>25</v>
+      </c>
+      <c r="G8" s="11">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3">
+        <v>35</v>
+      </c>
+      <c r="I8" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <f>SUM(F8:J8)</f>
+        <v>89.5</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="62" customHeight="1">
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="340" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3">
+        <v>19</v>
+      </c>
+      <c r="H9" s="3">
+        <v>34</v>
+      </c>
+      <c r="I9" s="3">
+        <v>24</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" ht="25" customHeight="1">
       <c r="A10" s="4"/>

--- a/HW6/HW6_submissions/HW6_grades.xlsx
+++ b/HW6/HW6_submissions/HW6_grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW6/HW6_submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D381E62-CCC6-6445-8A93-9A533A66E7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97847E2-E586-794B-BEEF-02C5EA1CC3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -173,85 +173,6 @@
   <si>
     <r>
       <t xml:space="preserve">Q1
-1) individual-level raw parameter prior </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주석처리함 (-5)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Q2
-Q3
-1) individual-level raw parameter prior </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주석처리함 (-5)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Q4
-1) individual-level raw parameter prior </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주석처리함 (-5)
-Q5
-1) 실행 코드에서 trial loop 누락/오류 (T정의를 안함) (-4)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Q1
-1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
-2a) ind posterior dist 없음 (-1)
-Q2
-1) beta prior 설정 0~5 (-1)
-Q3
-1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
-2) ind posterior dist 없음 (-1)
-Q4
-1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
-1) ind post distribution 없음 (-1)
-Q5
-1) 문제없음 
-2) 문제없음</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Q1
 2a) individual posterior distribution </t>
     </r>
     <r>
@@ -1005,6 +926,22 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Q1
+1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
+2a) ind posterior dist 없음 (-1)
+Q2
+Q3
+1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
+2) ind posterior dist 없음 (-1)
+Q4
+1) geneterated quantities mu_alpha, mu_beta 정의 없음 (-5)
+1) ind post distribution 없음 (-1)
+Q5
+1) 문제없음 
+2) 문제없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1026,11 +963,11 @@
       </rPr>
       <t xml:space="preserve">
 Q1
-1) stan 에서 alpha_pr, beta_pr 주석 처리 (-5)
+1) stan 에서 hyperparameter 주석 처리 (-5)
 Q2
 1) beta unifiorm prior 설정 0~5 (-1)
 Q3
-1) stan 에서 alpha_pr, beta_pr 주석 처리 (-5)
+1) stan 에서 hyperparameter 주석 처리 (-5)
 Q4
 1) stan 에 hyperparameter(alpha_pos, alpha_neg, beta) 없음 (-2.5)
 2) 없음(-5) 
@@ -1038,6 +975,28 @@
 4) 없음 (-10)
 Q5
 없음</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Q1
+Q2
+Q3
+Q4
+1) individual-level raw parameter prior </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주석처리함 (-5)
+Q5
+1) 실행 코드에서 trial loop 누락/오류 (T정의를 안함) (-4)</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1581,7 +1540,7 @@
         <v>141.5</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" ht="281" customHeight="1">
@@ -1620,7 +1579,7 @@
         <v>131</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" ht="401" customHeight="1">
@@ -1659,7 +1618,7 @@
         <v>108</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" ht="119" customHeight="1">
@@ -1735,7 +1694,7 @@
         <v>132</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="1" ht="244" customHeight="1">
@@ -1774,7 +1733,7 @@
         <v>146</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="1" ht="324" customHeight="1">
@@ -1813,7 +1772,7 @@
         <v>89.5</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="1" customFormat="1" ht="340" customHeight="1">
@@ -1852,7 +1811,7 @@
         <v>101</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" ht="25" customHeight="1">
